--- a/branches/cpg-guidance/ValueSet-condition-valueset.xlsx
+++ b/branches/cpg-guidance/ValueSet-condition-valueset.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T15:33:45+00:00</t>
+    <t>2024-12-11T16:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-guidance/ValueSet-condition-valueset.xlsx
+++ b/branches/cpg-guidance/ValueSet-condition-valueset.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T16:17:48+00:00</t>
+    <t>2024-12-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-guidance/ValueSet-condition-valueset.xlsx
+++ b/branches/cpg-guidance/ValueSet-condition-valueset.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T15:55:45+00:00</t>
+    <t>2024-12-23T16:34:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
